--- a/app/模板/结算模板/【大连游者之家】结算单_《X3.X6.闪暖》2026年4月模板.xlsx
+++ b/app/模板/结算模板/【大连游者之家】结算单_《X3.X6.闪暖》2026年4月模板.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\baojia\electron\app\模板\结算模板\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12240"/>
   </bookViews>
@@ -2180,7 +2185,7 @@
       <c r="E24" s="59"/>
       <c r="F24" s="59"/>
       <c r="G24" s="60">
-        <f>SUM(G10:G23)</f>
+        <f>ROUND(SUM(G10:G23),0)</f>
         <v>11248</v>
       </c>
       <c r="H24" s="63"/>
